--- a/points_previous.xlsx
+++ b/points_previous.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Data\workspace\PS_EC_AI\AI_CodeCoverage\T20Dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4A75F5F-F7E5-4132-8B9F-76C38C5DAE72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{219E7699-FFF7-40A3-8A2F-0C81F0D23925}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
   <si>
     <t>Name</t>
   </si>
@@ -128,6 +128,18 @@
   </si>
   <si>
     <t>Poll20_INDvsZIM_Margin</t>
+  </si>
+  <si>
+    <t>Poll21_ENGvsNZ</t>
+  </si>
+  <si>
+    <t>Anoop MK</t>
+  </si>
+  <si>
+    <t>Poll22_ENGvsNZ_Margin</t>
+  </si>
+  <si>
+    <t>Poll2_Group2_Top</t>
   </si>
 </sst>
 </file>
@@ -467,22 +479,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q20"/>
+  <dimension ref="A1:T21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.5703125" customWidth="1"/>
-    <col min="2" max="2" width="14.28515625" hidden="1" customWidth="1"/>
-    <col min="3" max="3" width="19.5703125" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" hidden="1" customWidth="1"/>
-    <col min="5" max="5" width="20.7109375" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="16.140625" hidden="1" customWidth="1"/>
-    <col min="7" max="7" width="21.140625" hidden="1" customWidth="1"/>
-    <col min="8" max="8" width="14.140625" hidden="1" customWidth="1"/>
-    <col min="9" max="9" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.5703125" customWidth="1"/>
+    <col min="3" max="3" width="7.42578125" customWidth="1"/>
+    <col min="4" max="4" width="7.7109375" customWidth="1"/>
+    <col min="5" max="5" width="7.28515625" customWidth="1"/>
+    <col min="6" max="6" width="7.7109375" customWidth="1"/>
+    <col min="7" max="7" width="6.7109375" customWidth="1"/>
+    <col min="8" max="8" width="5.5703125" customWidth="1"/>
+    <col min="9" max="9" width="5.85546875" customWidth="1"/>
     <col min="14" max="14" width="9.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -534,8 +546,17 @@
       <c r="Q1" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R1" t="s">
+        <v>36</v>
+      </c>
+      <c r="S1" t="s">
+        <v>38</v>
+      </c>
+      <c r="T1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -587,8 +608,17 @@
       <c r="Q2">
         <v>5</v>
       </c>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0</v>
+      </c>
+      <c r="T2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -640,8 +670,17 @@
       <c r="Q3">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R3">
+        <v>0</v>
+      </c>
+      <c r="S3">
+        <v>0</v>
+      </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -693,8 +732,17 @@
       <c r="Q4">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R4">
+        <v>0</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -746,8 +794,17 @@
       <c r="Q5">
         <v>5</v>
       </c>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R5">
+        <v>0</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -799,8 +856,17 @@
       <c r="Q6">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R6">
+        <v>3</v>
+      </c>
+      <c r="S6">
+        <v>0</v>
+      </c>
+      <c r="T6">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -852,8 +918,17 @@
       <c r="Q7">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R7">
+        <v>3</v>
+      </c>
+      <c r="S7">
+        <v>4</v>
+      </c>
+      <c r="T7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -905,8 +980,17 @@
       <c r="Q8">
         <v>5</v>
       </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R8">
+        <v>0</v>
+      </c>
+      <c r="S8">
+        <v>0</v>
+      </c>
+      <c r="T8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>10</v>
       </c>
@@ -958,8 +1042,17 @@
       <c r="Q9">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R9">
+        <v>0</v>
+      </c>
+      <c r="S9">
+        <v>0</v>
+      </c>
+      <c r="T9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>11</v>
       </c>
@@ -1011,8 +1104,17 @@
       <c r="Q10">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R10">
+        <v>0</v>
+      </c>
+      <c r="S10">
+        <v>0</v>
+      </c>
+      <c r="T10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>12</v>
       </c>
@@ -1064,8 +1166,17 @@
       <c r="Q11">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R11">
+        <v>0</v>
+      </c>
+      <c r="S11">
+        <v>0</v>
+      </c>
+      <c r="T11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>13</v>
       </c>
@@ -1117,8 +1228,17 @@
       <c r="Q12">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R12">
+        <v>0</v>
+      </c>
+      <c r="S12">
+        <v>0</v>
+      </c>
+      <c r="T12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>14</v>
       </c>
@@ -1170,8 +1290,17 @@
       <c r="Q13">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R13">
+        <v>0</v>
+      </c>
+      <c r="S13">
+        <v>0</v>
+      </c>
+      <c r="T13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>15</v>
       </c>
@@ -1223,8 +1352,17 @@
       <c r="Q14">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R14">
+        <v>0</v>
+      </c>
+      <c r="S14">
+        <v>0</v>
+      </c>
+      <c r="T14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>16</v>
       </c>
@@ -1276,8 +1414,17 @@
       <c r="Q15">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R15">
+        <v>0</v>
+      </c>
+      <c r="S15">
+        <v>0</v>
+      </c>
+      <c r="T15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>17</v>
       </c>
@@ -1329,8 +1476,17 @@
       <c r="Q16">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R16">
+        <v>0</v>
+      </c>
+      <c r="S16">
+        <v>0</v>
+      </c>
+      <c r="T16">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="17" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>18</v>
       </c>
@@ -1382,8 +1538,17 @@
       <c r="Q17">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R17">
+        <v>0</v>
+      </c>
+      <c r="S17">
+        <v>0</v>
+      </c>
+      <c r="T17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>19</v>
       </c>
@@ -1435,8 +1600,17 @@
       <c r="Q18">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R18">
+        <v>0</v>
+      </c>
+      <c r="S18">
+        <v>0</v>
+      </c>
+      <c r="T18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>20</v>
       </c>
@@ -1488,8 +1662,17 @@
       <c r="Q19">
         <v>0</v>
       </c>
-    </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R19">
+        <v>0</v>
+      </c>
+      <c r="S19">
+        <v>0</v>
+      </c>
+      <c r="T19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>21</v>
       </c>
@@ -1540,6 +1723,77 @@
       </c>
       <c r="Q20">
         <v>5</v>
+      </c>
+      <c r="R20">
+        <v>3</v>
+      </c>
+      <c r="S20">
+        <v>0</v>
+      </c>
+      <c r="T20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>37</v>
+      </c>
+      <c r="B21">
+        <v>0</v>
+      </c>
+      <c r="C21">
+        <v>0</v>
+      </c>
+      <c r="D21">
+        <v>0</v>
+      </c>
+      <c r="E21">
+        <v>0</v>
+      </c>
+      <c r="F21">
+        <v>0</v>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="H21">
+        <v>0</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>0</v>
+      </c>
+      <c r="K21">
+        <v>0</v>
+      </c>
+      <c r="L21">
+        <v>0</v>
+      </c>
+      <c r="M21">
+        <v>0</v>
+      </c>
+      <c r="N21">
+        <v>0</v>
+      </c>
+      <c r="O21">
+        <v>0</v>
+      </c>
+      <c r="P21">
+        <v>0</v>
+      </c>
+      <c r="Q21">
+        <v>0</v>
+      </c>
+      <c r="R21">
+        <v>3</v>
+      </c>
+      <c r="S21">
+        <v>0</v>
+      </c>
+      <c r="T21">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/points_previous.xlsx
+++ b/points_previous.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Data\workspace\PS_EC_AI\AI_CodeCoverage\T20Dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{219E7699-FFF7-40A3-8A2F-0C81F0D23925}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C3CD966-AF8C-48E1-BE89-1B3683AE78B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="49">
   <si>
     <t>Name</t>
   </si>
@@ -139,7 +139,34 @@
     <t>Poll22_ENGvsNZ_Margin</t>
   </si>
   <si>
-    <t>Poll2_Group2_Top</t>
+    <t>Poll10_Group2_Top</t>
+  </si>
+  <si>
+    <t>Poll9_Group1_Top</t>
+  </si>
+  <si>
+    <t>Poll11_Semifinalist</t>
+  </si>
+  <si>
+    <t>Ramithash</t>
+  </si>
+  <si>
+    <t>Poll23_SL_PAK</t>
+  </si>
+  <si>
+    <t>Poll24_SL_PAK_Margin</t>
+  </si>
+  <si>
+    <t>Poll26_INDvsWI</t>
+  </si>
+  <si>
+    <t>Poll28_INDvsWI_Margin</t>
+  </si>
+  <si>
+    <t>Poll25_ZIM_SA</t>
+  </si>
+  <si>
+    <t>Poll27_ZIM_SA_Margin</t>
   </si>
 </sst>
 </file>
@@ -479,7 +506,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T21"/>
+  <dimension ref="A1:AB22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.5703125" customWidth="1"/>
@@ -494,7 +521,7 @@
     <col min="14" max="14" width="9.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -553,10 +580,34 @@
         <v>38</v>
       </c>
       <c r="T1" t="s">
+        <v>40</v>
+      </c>
+      <c r="U1" t="s">
         <v>39</v>
       </c>
+      <c r="V1" t="s">
+        <v>41</v>
+      </c>
+      <c r="W1" t="s">
+        <v>43</v>
+      </c>
+      <c r="X1" t="s">
+        <v>44</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>47</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>48</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>45</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>46</v>
+      </c>
     </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -617,8 +668,32 @@
       <c r="T2">
         <v>7</v>
       </c>
+      <c r="U2">
+        <v>7</v>
+      </c>
+      <c r="V2">
+        <v>15</v>
+      </c>
+      <c r="W2">
+        <v>0</v>
+      </c>
+      <c r="X2">
+        <v>0</v>
+      </c>
+      <c r="Y2">
+        <v>3</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+      <c r="AA2">
+        <v>3</v>
+      </c>
+      <c r="AB2">
+        <v>0</v>
+      </c>
     </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -679,8 +754,32 @@
       <c r="T3">
         <v>0</v>
       </c>
+      <c r="U3">
+        <v>0</v>
+      </c>
+      <c r="V3">
+        <v>10</v>
+      </c>
+      <c r="W3">
+        <v>0</v>
+      </c>
+      <c r="X3">
+        <v>0</v>
+      </c>
+      <c r="Y3">
+        <v>3</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+      <c r="AA3">
+        <v>3</v>
+      </c>
+      <c r="AB3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -739,10 +838,34 @@
         <v>0</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>7</v>
+      </c>
+      <c r="U4">
+        <v>0</v>
+      </c>
+      <c r="V4">
+        <v>10</v>
+      </c>
+      <c r="W4">
+        <v>0</v>
+      </c>
+      <c r="X4">
+        <v>0</v>
+      </c>
+      <c r="Y4">
+        <v>3</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+      <c r="AA4">
+        <v>3</v>
+      </c>
+      <c r="AB4">
+        <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -801,10 +924,34 @@
         <v>0</v>
       </c>
       <c r="T5">
+        <v>7</v>
+      </c>
+      <c r="U5">
+        <v>0</v>
+      </c>
+      <c r="V5">
+        <v>15</v>
+      </c>
+      <c r="W5">
+        <v>3</v>
+      </c>
+      <c r="X5">
+        <v>0</v>
+      </c>
+      <c r="Y5">
+        <v>3</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+      <c r="AA5">
+        <v>3</v>
+      </c>
+      <c r="AB5">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -865,8 +1012,32 @@
       <c r="T6">
         <v>7</v>
       </c>
+      <c r="U6">
+        <v>7</v>
+      </c>
+      <c r="V6">
+        <v>10</v>
+      </c>
+      <c r="W6">
+        <v>0</v>
+      </c>
+      <c r="X6">
+        <v>0</v>
+      </c>
+      <c r="Y6">
+        <v>3</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+      <c r="AA6">
+        <v>3</v>
+      </c>
+      <c r="AB6">
+        <v>0</v>
+      </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -927,8 +1098,32 @@
       <c r="T7">
         <v>0</v>
       </c>
+      <c r="U7">
+        <v>0</v>
+      </c>
+      <c r="V7">
+        <v>0</v>
+      </c>
+      <c r="W7">
+        <v>3</v>
+      </c>
+      <c r="X7">
+        <v>0</v>
+      </c>
+      <c r="Y7">
+        <v>3</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+      <c r="AA7">
+        <v>3</v>
+      </c>
+      <c r="AB7">
+        <v>0</v>
+      </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -987,10 +1182,34 @@
         <v>0</v>
       </c>
       <c r="T8">
+        <v>7</v>
+      </c>
+      <c r="U8">
+        <v>0</v>
+      </c>
+      <c r="V8">
+        <v>15</v>
+      </c>
+      <c r="W8">
+        <v>3</v>
+      </c>
+      <c r="X8">
+        <v>0</v>
+      </c>
+      <c r="Y8">
+        <v>3</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+      <c r="AA8">
+        <v>3</v>
+      </c>
+      <c r="AB8">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>10</v>
       </c>
@@ -1049,10 +1268,34 @@
         <v>0</v>
       </c>
       <c r="T9">
+        <v>7</v>
+      </c>
+      <c r="U9">
+        <v>0</v>
+      </c>
+      <c r="V9">
+        <v>10</v>
+      </c>
+      <c r="W9">
+        <v>3</v>
+      </c>
+      <c r="X9">
+        <v>4</v>
+      </c>
+      <c r="Y9">
+        <v>3</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+      <c r="AA9">
+        <v>0</v>
+      </c>
+      <c r="AB9">
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>11</v>
       </c>
@@ -1113,8 +1356,32 @@
       <c r="T10">
         <v>0</v>
       </c>
+      <c r="U10">
+        <v>0</v>
+      </c>
+      <c r="V10">
+        <v>10</v>
+      </c>
+      <c r="W10">
+        <v>0</v>
+      </c>
+      <c r="X10">
+        <v>0</v>
+      </c>
+      <c r="Y10">
+        <v>3</v>
+      </c>
+      <c r="Z10">
+        <v>3</v>
+      </c>
+      <c r="AA10">
+        <v>3</v>
+      </c>
+      <c r="AB10">
+        <v>0</v>
+      </c>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>12</v>
       </c>
@@ -1175,8 +1442,32 @@
       <c r="T11">
         <v>0</v>
       </c>
+      <c r="U11">
+        <v>0</v>
+      </c>
+      <c r="V11">
+        <v>0</v>
+      </c>
+      <c r="W11">
+        <v>0</v>
+      </c>
+      <c r="X11">
+        <v>0</v>
+      </c>
+      <c r="Y11">
+        <v>0</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+      <c r="AA11">
+        <v>0</v>
+      </c>
+      <c r="AB11">
+        <v>0</v>
+      </c>
     </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>13</v>
       </c>
@@ -1237,8 +1528,32 @@
       <c r="T12">
         <v>0</v>
       </c>
+      <c r="U12">
+        <v>0</v>
+      </c>
+      <c r="V12">
+        <v>0</v>
+      </c>
+      <c r="W12">
+        <v>0</v>
+      </c>
+      <c r="X12">
+        <v>0</v>
+      </c>
+      <c r="Y12">
+        <v>3</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+      <c r="AA12">
+        <v>3</v>
+      </c>
+      <c r="AB12">
+        <v>4</v>
+      </c>
     </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>14</v>
       </c>
@@ -1299,8 +1614,32 @@
       <c r="T13">
         <v>0</v>
       </c>
+      <c r="U13">
+        <v>0</v>
+      </c>
+      <c r="V13">
+        <v>0</v>
+      </c>
+      <c r="W13">
+        <v>0</v>
+      </c>
+      <c r="X13">
+        <v>0</v>
+      </c>
+      <c r="Y13">
+        <v>3</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+      <c r="AA13">
+        <v>3</v>
+      </c>
+      <c r="AB13">
+        <v>4</v>
+      </c>
     </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>15</v>
       </c>
@@ -1361,8 +1700,32 @@
       <c r="T14">
         <v>0</v>
       </c>
+      <c r="U14">
+        <v>0</v>
+      </c>
+      <c r="V14">
+        <v>0</v>
+      </c>
+      <c r="W14">
+        <v>0</v>
+      </c>
+      <c r="X14">
+        <v>0</v>
+      </c>
+      <c r="Y14">
+        <v>0</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+      <c r="AA14">
+        <v>0</v>
+      </c>
+      <c r="AB14">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>16</v>
       </c>
@@ -1423,8 +1786,32 @@
       <c r="T15">
         <v>0</v>
       </c>
+      <c r="U15">
+        <v>0</v>
+      </c>
+      <c r="V15">
+        <v>0</v>
+      </c>
+      <c r="W15">
+        <v>0</v>
+      </c>
+      <c r="X15">
+        <v>0</v>
+      </c>
+      <c r="Y15">
+        <v>0</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+      <c r="AA15">
+        <v>0</v>
+      </c>
+      <c r="AB15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>17</v>
       </c>
@@ -1485,8 +1872,32 @@
       <c r="T16">
         <v>7</v>
       </c>
+      <c r="U16">
+        <v>7</v>
+      </c>
+      <c r="V16">
+        <v>10</v>
+      </c>
+      <c r="W16">
+        <v>0</v>
+      </c>
+      <c r="X16">
+        <v>0</v>
+      </c>
+      <c r="Y16">
+        <v>3</v>
+      </c>
+      <c r="Z16">
+        <v>3</v>
+      </c>
+      <c r="AA16">
+        <v>3</v>
+      </c>
+      <c r="AB16">
+        <v>4</v>
+      </c>
     </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>18</v>
       </c>
@@ -1547,8 +1958,32 @@
       <c r="T17">
         <v>0</v>
       </c>
+      <c r="U17">
+        <v>0</v>
+      </c>
+      <c r="V17">
+        <v>0</v>
+      </c>
+      <c r="W17">
+        <v>0</v>
+      </c>
+      <c r="X17">
+        <v>0</v>
+      </c>
+      <c r="Y17">
+        <v>3</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+      <c r="AA17">
+        <v>3</v>
+      </c>
+      <c r="AB17">
+        <v>4</v>
+      </c>
     </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>19</v>
       </c>
@@ -1609,8 +2044,32 @@
       <c r="T18">
         <v>0</v>
       </c>
+      <c r="U18">
+        <v>0</v>
+      </c>
+      <c r="V18">
+        <v>0</v>
+      </c>
+      <c r="W18">
+        <v>0</v>
+      </c>
+      <c r="X18">
+        <v>0</v>
+      </c>
+      <c r="Y18">
+        <v>0</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+      <c r="AA18">
+        <v>0</v>
+      </c>
+      <c r="AB18">
+        <v>0</v>
+      </c>
     </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>20</v>
       </c>
@@ -1671,8 +2130,32 @@
       <c r="T19">
         <v>0</v>
       </c>
+      <c r="U19">
+        <v>0</v>
+      </c>
+      <c r="V19">
+        <v>0</v>
+      </c>
+      <c r="W19">
+        <v>3</v>
+      </c>
+      <c r="X19">
+        <v>0</v>
+      </c>
+      <c r="Y19">
+        <v>3</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+      <c r="AA19">
+        <v>3</v>
+      </c>
+      <c r="AB19">
+        <v>4</v>
+      </c>
     </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>21</v>
       </c>
@@ -1733,8 +2216,32 @@
       <c r="T20">
         <v>0</v>
       </c>
+      <c r="U20">
+        <v>0</v>
+      </c>
+      <c r="V20">
+        <v>6</v>
+      </c>
+      <c r="W20">
+        <v>0</v>
+      </c>
+      <c r="X20">
+        <v>0</v>
+      </c>
+      <c r="Y20">
+        <v>0</v>
+      </c>
+      <c r="Z20">
+        <v>3</v>
+      </c>
+      <c r="AA20">
+        <v>3</v>
+      </c>
+      <c r="AB20">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>37</v>
       </c>
@@ -1793,6 +2300,116 @@
         <v>0</v>
       </c>
       <c r="T21">
+        <v>0</v>
+      </c>
+      <c r="U21">
+        <v>0</v>
+      </c>
+      <c r="V21">
+        <v>0</v>
+      </c>
+      <c r="W21">
+        <v>0</v>
+      </c>
+      <c r="X21">
+        <v>0</v>
+      </c>
+      <c r="Y21">
+        <v>0</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+      <c r="AA21">
+        <v>0</v>
+      </c>
+      <c r="AB21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>42</v>
+      </c>
+      <c r="B22">
+        <v>0</v>
+      </c>
+      <c r="C22">
+        <v>0</v>
+      </c>
+      <c r="D22">
+        <v>0</v>
+      </c>
+      <c r="E22">
+        <v>0</v>
+      </c>
+      <c r="F22">
+        <v>0</v>
+      </c>
+      <c r="G22">
+        <v>0</v>
+      </c>
+      <c r="H22">
+        <v>0</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>0</v>
+      </c>
+      <c r="K22">
+        <v>0</v>
+      </c>
+      <c r="L22">
+        <v>0</v>
+      </c>
+      <c r="M22">
+        <v>0</v>
+      </c>
+      <c r="N22">
+        <v>0</v>
+      </c>
+      <c r="O22">
+        <v>0</v>
+      </c>
+      <c r="P22">
+        <v>0</v>
+      </c>
+      <c r="Q22">
+        <v>0</v>
+      </c>
+      <c r="R22">
+        <v>0</v>
+      </c>
+      <c r="S22">
+        <v>0</v>
+      </c>
+      <c r="T22">
+        <v>0</v>
+      </c>
+      <c r="U22">
+        <v>0</v>
+      </c>
+      <c r="V22">
+        <v>10</v>
+      </c>
+      <c r="W22">
+        <v>0</v>
+      </c>
+      <c r="X22">
+        <v>0</v>
+      </c>
+      <c r="Y22">
+        <v>0</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+      <c r="AA22">
+        <v>0</v>
+      </c>
+      <c r="AB22">
         <v>0</v>
       </c>
     </row>

--- a/points_previous.xlsx
+++ b/points_previous.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Data\workspace\PS_EC_AI\AI_CodeCoverage\T20Dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C3CD966-AF8C-48E1-BE89-1B3683AE78B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B4BC020-6AE5-41DD-89EF-A78918722F08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="59">
   <si>
     <t>Name</t>
   </si>
@@ -167,6 +167,36 @@
   </si>
   <si>
     <t>Poll27_ZIM_SA_Margin</t>
+  </si>
+  <si>
+    <t>Poll16_Finalist</t>
+  </si>
+  <si>
+    <t>Poll29_Finalist</t>
+  </si>
+  <si>
+    <t>poll31_SAvsNZ</t>
+  </si>
+  <si>
+    <t>Sujeesh</t>
+  </si>
+  <si>
+    <t>Bejoy</t>
+  </si>
+  <si>
+    <t>poll32_SAvsNZ_Score</t>
+  </si>
+  <si>
+    <t>poll33_NZvsSA_Sixers</t>
+  </si>
+  <si>
+    <t>poll34_INDvsENG</t>
+  </si>
+  <si>
+    <t>poll35_INDvsENG_Score</t>
+  </si>
+  <si>
+    <t>poll36_INDvsENG_Sixers</t>
   </si>
 </sst>
 </file>
@@ -506,22 +536,25 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AB22"/>
+  <dimension ref="A1:AJ24"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.5703125" customWidth="1"/>
-    <col min="2" max="2" width="7.5703125" customWidth="1"/>
-    <col min="3" max="3" width="7.42578125" customWidth="1"/>
-    <col min="4" max="4" width="7.7109375" customWidth="1"/>
-    <col min="5" max="5" width="7.28515625" customWidth="1"/>
-    <col min="6" max="6" width="7.7109375" customWidth="1"/>
-    <col min="7" max="7" width="6.7109375" customWidth="1"/>
-    <col min="8" max="8" width="5.5703125" customWidth="1"/>
-    <col min="9" max="9" width="5.85546875" customWidth="1"/>
-    <col min="14" max="14" width="9.7109375" customWidth="1"/>
+    <col min="1" max="1" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.5703125" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="7.42578125" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="7.7109375" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="7.28515625" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="7.7109375" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="6.7109375" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="5.5703125" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="5.85546875" hidden="1" customWidth="1"/>
+    <col min="10" max="13" width="0" hidden="1" customWidth="1"/>
+    <col min="14" max="14" width="9.7109375" hidden="1" customWidth="1"/>
+    <col min="15" max="27" width="0" hidden="1" customWidth="1"/>
+    <col min="28" max="28" width="22.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -606,8 +639,32 @@
       <c r="AB1" t="s">
         <v>46</v>
       </c>
+      <c r="AC1" t="s">
+        <v>49</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>50</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>51</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>54</v>
+      </c>
+      <c r="AG1" t="s">
+        <v>55</v>
+      </c>
+      <c r="AH1" t="s">
+        <v>56</v>
+      </c>
+      <c r="AI1" t="s">
+        <v>57</v>
+      </c>
+      <c r="AJ1" t="s">
+        <v>58</v>
+      </c>
     </row>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -692,8 +749,32 @@
       <c r="AB2">
         <v>0</v>
       </c>
+      <c r="AC2">
+        <v>0</v>
+      </c>
+      <c r="AD2">
+        <v>12</v>
+      </c>
+      <c r="AE2">
+        <v>5</v>
+      </c>
+      <c r="AF2">
+        <v>0</v>
+      </c>
+      <c r="AG2">
+        <v>0</v>
+      </c>
+      <c r="AH2">
+        <v>5</v>
+      </c>
+      <c r="AI2">
+        <v>0</v>
+      </c>
+      <c r="AJ2">
+        <v>0</v>
+      </c>
     </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -778,8 +859,32 @@
       <c r="AB3">
         <v>0</v>
       </c>
+      <c r="AC3">
+        <v>5</v>
+      </c>
+      <c r="AD3">
+        <v>5</v>
+      </c>
+      <c r="AE3">
+        <v>5</v>
+      </c>
+      <c r="AF3">
+        <v>0</v>
+      </c>
+      <c r="AG3">
+        <v>6</v>
+      </c>
+      <c r="AH3">
+        <v>5</v>
+      </c>
+      <c r="AI3">
+        <v>0</v>
+      </c>
+      <c r="AJ3">
+        <v>6</v>
+      </c>
     </row>
-    <row r="4" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -864,8 +969,32 @@
       <c r="AB4">
         <v>4</v>
       </c>
+      <c r="AC4">
+        <v>0</v>
+      </c>
+      <c r="AD4">
+        <v>5</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>4</v>
+      </c>
+      <c r="AG4">
+        <v>0</v>
+      </c>
+      <c r="AH4">
+        <v>5</v>
+      </c>
+      <c r="AI4">
+        <v>0</v>
+      </c>
+      <c r="AJ4">
+        <v>0</v>
+      </c>
     </row>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -950,8 +1079,32 @@
       <c r="AB5">
         <v>0</v>
       </c>
+      <c r="AC5">
+        <v>5</v>
+      </c>
+      <c r="AD5">
+        <v>5</v>
+      </c>
+      <c r="AE5">
+        <v>0</v>
+      </c>
+      <c r="AF5">
+        <v>0</v>
+      </c>
+      <c r="AG5">
+        <v>0</v>
+      </c>
+      <c r="AH5">
+        <v>5</v>
+      </c>
+      <c r="AI5">
+        <v>0</v>
+      </c>
+      <c r="AJ5">
+        <v>6</v>
+      </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -1036,8 +1189,32 @@
       <c r="AB6">
         <v>0</v>
       </c>
+      <c r="AC6">
+        <v>0</v>
+      </c>
+      <c r="AD6">
+        <v>5</v>
+      </c>
+      <c r="AE6">
+        <v>5</v>
+      </c>
+      <c r="AF6">
+        <v>0</v>
+      </c>
+      <c r="AG6">
+        <v>0</v>
+      </c>
+      <c r="AH6">
+        <v>5</v>
+      </c>
+      <c r="AI6">
+        <v>0</v>
+      </c>
+      <c r="AJ6">
+        <v>0</v>
+      </c>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -1122,8 +1299,32 @@
       <c r="AB7">
         <v>0</v>
       </c>
+      <c r="AC7">
+        <v>0</v>
+      </c>
+      <c r="AD7">
+        <v>5</v>
+      </c>
+      <c r="AE7">
+        <v>0</v>
+      </c>
+      <c r="AF7">
+        <v>4</v>
+      </c>
+      <c r="AG7">
+        <v>6</v>
+      </c>
+      <c r="AH7">
+        <v>5</v>
+      </c>
+      <c r="AI7">
+        <v>0</v>
+      </c>
+      <c r="AJ7">
+        <v>0</v>
+      </c>
     </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -1208,8 +1409,32 @@
       <c r="AB8">
         <v>0</v>
       </c>
+      <c r="AC8">
+        <v>5</v>
+      </c>
+      <c r="AD8">
+        <v>5</v>
+      </c>
+      <c r="AE8">
+        <v>0</v>
+      </c>
+      <c r="AF8">
+        <v>0</v>
+      </c>
+      <c r="AG8">
+        <v>0</v>
+      </c>
+      <c r="AH8">
+        <v>5</v>
+      </c>
+      <c r="AI8">
+        <v>6</v>
+      </c>
+      <c r="AJ8">
+        <v>6</v>
+      </c>
     </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>10</v>
       </c>
@@ -1294,8 +1519,32 @@
       <c r="AB9">
         <v>0</v>
       </c>
+      <c r="AC9">
+        <v>5</v>
+      </c>
+      <c r="AD9">
+        <v>5</v>
+      </c>
+      <c r="AE9">
+        <v>5</v>
+      </c>
+      <c r="AF9">
+        <v>0</v>
+      </c>
+      <c r="AG9">
+        <v>0</v>
+      </c>
+      <c r="AH9">
+        <v>5</v>
+      </c>
+      <c r="AI9">
+        <v>6</v>
+      </c>
+      <c r="AJ9">
+        <v>6</v>
+      </c>
     </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>11</v>
       </c>
@@ -1380,8 +1629,32 @@
       <c r="AB10">
         <v>0</v>
       </c>
+      <c r="AC10">
+        <v>5</v>
+      </c>
+      <c r="AD10">
+        <v>5</v>
+      </c>
+      <c r="AE10">
+        <v>0</v>
+      </c>
+      <c r="AF10">
+        <v>4</v>
+      </c>
+      <c r="AG10">
+        <v>0</v>
+      </c>
+      <c r="AH10">
+        <v>5</v>
+      </c>
+      <c r="AI10">
+        <v>0</v>
+      </c>
+      <c r="AJ10">
+        <v>0</v>
+      </c>
     </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>12</v>
       </c>
@@ -1466,8 +1739,32 @@
       <c r="AB11">
         <v>0</v>
       </c>
+      <c r="AC11">
+        <v>0</v>
+      </c>
+      <c r="AD11">
+        <v>0</v>
+      </c>
+      <c r="AE11">
+        <v>0</v>
+      </c>
+      <c r="AF11">
+        <v>0</v>
+      </c>
+      <c r="AG11">
+        <v>0</v>
+      </c>
+      <c r="AH11">
+        <v>0</v>
+      </c>
+      <c r="AI11">
+        <v>0</v>
+      </c>
+      <c r="AJ11">
+        <v>0</v>
+      </c>
     </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>13</v>
       </c>
@@ -1552,8 +1849,32 @@
       <c r="AB12">
         <v>4</v>
       </c>
+      <c r="AC12">
+        <v>0</v>
+      </c>
+      <c r="AD12">
+        <v>5</v>
+      </c>
+      <c r="AE12">
+        <v>0</v>
+      </c>
+      <c r="AF12">
+        <v>0</v>
+      </c>
+      <c r="AG12">
+        <v>0</v>
+      </c>
+      <c r="AH12">
+        <v>5</v>
+      </c>
+      <c r="AI12">
+        <v>0</v>
+      </c>
+      <c r="AJ12">
+        <v>0</v>
+      </c>
     </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>14</v>
       </c>
@@ -1638,8 +1959,32 @@
       <c r="AB13">
         <v>4</v>
       </c>
+      <c r="AC13">
+        <v>5</v>
+      </c>
+      <c r="AD13">
+        <v>0</v>
+      </c>
+      <c r="AE13">
+        <v>0</v>
+      </c>
+      <c r="AF13">
+        <v>0</v>
+      </c>
+      <c r="AG13">
+        <v>0</v>
+      </c>
+      <c r="AH13">
+        <v>5</v>
+      </c>
+      <c r="AI13">
+        <v>0</v>
+      </c>
+      <c r="AJ13">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>15</v>
       </c>
@@ -1724,8 +2069,32 @@
       <c r="AB14">
         <v>0</v>
       </c>
+      <c r="AC14">
+        <v>0</v>
+      </c>
+      <c r="AD14">
+        <v>0</v>
+      </c>
+      <c r="AE14">
+        <v>0</v>
+      </c>
+      <c r="AF14">
+        <v>0</v>
+      </c>
+      <c r="AG14">
+        <v>0</v>
+      </c>
+      <c r="AH14">
+        <v>5</v>
+      </c>
+      <c r="AI14">
+        <v>0</v>
+      </c>
+      <c r="AJ14">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>16</v>
       </c>
@@ -1810,8 +2179,32 @@
       <c r="AB15">
         <v>0</v>
       </c>
+      <c r="AC15">
+        <v>0</v>
+      </c>
+      <c r="AD15">
+        <v>0</v>
+      </c>
+      <c r="AE15">
+        <v>0</v>
+      </c>
+      <c r="AF15">
+        <v>0</v>
+      </c>
+      <c r="AG15">
+        <v>0</v>
+      </c>
+      <c r="AH15">
+        <v>0</v>
+      </c>
+      <c r="AI15">
+        <v>0</v>
+      </c>
+      <c r="AJ15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>17</v>
       </c>
@@ -1896,8 +2289,32 @@
       <c r="AB16">
         <v>4</v>
       </c>
+      <c r="AC16">
+        <v>0</v>
+      </c>
+      <c r="AD16">
+        <v>5</v>
+      </c>
+      <c r="AE16">
+        <v>0</v>
+      </c>
+      <c r="AF16">
+        <v>0</v>
+      </c>
+      <c r="AG16">
+        <v>0</v>
+      </c>
+      <c r="AH16">
+        <v>5</v>
+      </c>
+      <c r="AI16">
+        <v>6</v>
+      </c>
+      <c r="AJ16">
+        <v>6</v>
+      </c>
     </row>
-    <row r="17" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>18</v>
       </c>
@@ -1982,8 +2399,32 @@
       <c r="AB17">
         <v>4</v>
       </c>
+      <c r="AC17">
+        <v>0</v>
+      </c>
+      <c r="AD17">
+        <v>5</v>
+      </c>
+      <c r="AE17">
+        <v>5</v>
+      </c>
+      <c r="AF17">
+        <v>0</v>
+      </c>
+      <c r="AG17">
+        <v>0</v>
+      </c>
+      <c r="AH17">
+        <v>5</v>
+      </c>
+      <c r="AI17">
+        <v>0</v>
+      </c>
+      <c r="AJ17">
+        <v>0</v>
+      </c>
     </row>
-    <row r="18" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>19</v>
       </c>
@@ -2068,8 +2509,32 @@
       <c r="AB18">
         <v>0</v>
       </c>
+      <c r="AC18">
+        <v>0</v>
+      </c>
+      <c r="AD18">
+        <v>0</v>
+      </c>
+      <c r="AE18">
+        <v>0</v>
+      </c>
+      <c r="AF18">
+        <v>0</v>
+      </c>
+      <c r="AG18">
+        <v>0</v>
+      </c>
+      <c r="AH18">
+        <v>0</v>
+      </c>
+      <c r="AI18">
+        <v>0</v>
+      </c>
+      <c r="AJ18">
+        <v>0</v>
+      </c>
     </row>
-    <row r="19" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>20</v>
       </c>
@@ -2154,8 +2619,32 @@
       <c r="AB19">
         <v>4</v>
       </c>
+      <c r="AC19">
+        <v>0</v>
+      </c>
+      <c r="AD19">
+        <v>0</v>
+      </c>
+      <c r="AE19">
+        <v>0</v>
+      </c>
+      <c r="AF19">
+        <v>0</v>
+      </c>
+      <c r="AG19">
+        <v>6</v>
+      </c>
+      <c r="AH19">
+        <v>5</v>
+      </c>
+      <c r="AI19">
+        <v>0</v>
+      </c>
+      <c r="AJ19">
+        <v>6</v>
+      </c>
     </row>
-    <row r="20" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>21</v>
       </c>
@@ -2240,8 +2729,32 @@
       <c r="AB20">
         <v>0</v>
       </c>
+      <c r="AC20">
+        <v>5</v>
+      </c>
+      <c r="AD20">
+        <v>5</v>
+      </c>
+      <c r="AE20">
+        <v>0</v>
+      </c>
+      <c r="AF20">
+        <v>0</v>
+      </c>
+      <c r="AG20">
+        <v>0</v>
+      </c>
+      <c r="AH20">
+        <v>5</v>
+      </c>
+      <c r="AI20">
+        <v>6</v>
+      </c>
+      <c r="AJ20">
+        <v>6</v>
+      </c>
     </row>
-    <row r="21" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>37</v>
       </c>
@@ -2326,8 +2839,32 @@
       <c r="AB21">
         <v>0</v>
       </c>
+      <c r="AC21">
+        <v>5</v>
+      </c>
+      <c r="AD21">
+        <v>0</v>
+      </c>
+      <c r="AE21">
+        <v>0</v>
+      </c>
+      <c r="AF21">
+        <v>0</v>
+      </c>
+      <c r="AG21">
+        <v>0</v>
+      </c>
+      <c r="AH21">
+        <v>0</v>
+      </c>
+      <c r="AI21">
+        <v>0</v>
+      </c>
+      <c r="AJ21">
+        <v>0</v>
+      </c>
     </row>
-    <row r="22" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>42</v>
       </c>
@@ -2410,6 +2947,94 @@
         <v>0</v>
       </c>
       <c r="AB22">
+        <v>0</v>
+      </c>
+      <c r="AC22">
+        <v>0</v>
+      </c>
+      <c r="AD22">
+        <v>0</v>
+      </c>
+      <c r="AE22">
+        <v>0</v>
+      </c>
+      <c r="AF22">
+        <v>0</v>
+      </c>
+      <c r="AG22">
+        <v>0</v>
+      </c>
+      <c r="AH22">
+        <v>0</v>
+      </c>
+      <c r="AI22">
+        <v>0</v>
+      </c>
+      <c r="AJ22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>52</v>
+      </c>
+      <c r="AB23">
+        <v>0</v>
+      </c>
+      <c r="AC23">
+        <v>0</v>
+      </c>
+      <c r="AD23">
+        <v>0</v>
+      </c>
+      <c r="AE23">
+        <v>5</v>
+      </c>
+      <c r="AF23">
+        <v>4</v>
+      </c>
+      <c r="AG23">
+        <v>0</v>
+      </c>
+      <c r="AH23">
+        <v>5</v>
+      </c>
+      <c r="AI23">
+        <v>0</v>
+      </c>
+      <c r="AJ23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>53</v>
+      </c>
+      <c r="AB24">
+        <v>0</v>
+      </c>
+      <c r="AC24">
+        <v>0</v>
+      </c>
+      <c r="AD24">
+        <v>0</v>
+      </c>
+      <c r="AE24">
+        <v>5</v>
+      </c>
+      <c r="AF24">
+        <v>0</v>
+      </c>
+      <c r="AG24">
+        <v>0</v>
+      </c>
+      <c r="AH24">
+        <v>0</v>
+      </c>
+      <c r="AI24">
+        <v>0</v>
+      </c>
+      <c r="AJ24">
         <v>0</v>
       </c>
     </row>
